--- a/case_settings/26-zone/CONUS_extra_inputs/conus_scenario_inputsBACKUP.xlsx
+++ b/case_settings/26-zone/CONUS_extra_inputs/conus_scenario_inputsBACKUP.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melek/Switch-USA-PG/MIP_results_comparison/case_settings/26-zone/CONUS_extra_inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melek/Documents/GitHub/Switch-USA-PG/MIP_results_comparison/case_settings/26-zone/CONUS_extra_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F91D14BC-6F25-4E43-8925-C9968B377C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
